--- a/Test/testdata.xlsx
+++ b/Test/testdata.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Name</t>
   </si>
@@ -40,6 +40,18 @@
   </si>
   <si>
     <t xml:space="preserve">Aufgabe 7</t>
+  </si>
+  <si>
+    <t>Kategorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kat 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kat 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kat 3 </t>
   </si>
   <si>
     <t>Gesamt</t>
@@ -681,92 +693,92 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>10</v>
-      </c>
-      <c r="H2" s="2">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
         <v>8</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H4" s="2">
         <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2">
-        <v>2</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -775,70 +787,70 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H6" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -850,33 +862,33 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H8" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -887,65 +899,65 @@
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
       </c>
       <c r="H10" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" t="s">
-        <v>18</v>
+      <c r="A12" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2">
         <v>4</v>
@@ -953,54 +965,54 @@
       <c r="E12" s="2">
         <v>3</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
+        <v>5</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13">
         <v>6</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G13" s="2">
         <v>8</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H13" s="2">
         <v>8</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2">
-        <v>5</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2</v>
-      </c>
-      <c r="F13" s="2">
-        <v>6</v>
-      </c>
-      <c r="G13" s="2">
-        <v>2</v>
-      </c>
-      <c r="H13" s="2">
-        <v>2</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2">
         <v>2</v>
@@ -1009,76 +1021,76 @@
         <v>6</v>
       </c>
       <c r="G14" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>6</v>
       </c>
       <c r="G15" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H15" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2">
-        <v>3</v>
-      </c>
-      <c r="F16" s="2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
       </c>
       <c r="G16" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H16" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
       </c>
       <c r="C17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2">
         <v>3</v>
@@ -1087,93 +1099,93 @@
         <v>3</v>
       </c>
       <c r="G17" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H17" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="2">
-        <v>2</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3</v>
       </c>
       <c r="G18" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H18" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2">
         <v>2</v>
       </c>
-      <c r="F19" s="2">
-        <v>5</v>
+      <c r="F19">
+        <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H20" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" t="s">
-        <v>27</v>
+      <c r="A21" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -1182,65 +1194,65 @@
         <v>4</v>
       </c>
       <c r="D21" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
+      <c r="A22" t="s">
+        <v>31</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
         <v>3</v>
       </c>
       <c r="F22" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" s="2">
         <v>3</v>
@@ -1251,13 +1263,13 @@
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
@@ -1266,38 +1278,64 @@
         <v>1</v>
       </c>
       <c r="F24" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2">
         <v>4</v>
       </c>
       <c r="G25" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2">
+        <v>4</v>
+      </c>
+      <c r="G26" s="2">
+        <v>10</v>
+      </c>
+      <c r="H26" s="2">
         <v>10</v>
       </c>
     </row>
